--- a/Flag/Flagar/lista_mos.xlsx
+++ b/Flag/Flagar/lista_mos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\le37118890\Desktop\codigos_amil\Codigos_Amil\Flag\Flagar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6061B0-28BA-404E-880C-E00C13E9F5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DCF01B8-DA0B-45EF-80BD-E9FE7D847D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
   <si>
     <t>Flag</t>
   </si>
@@ -454,11 +454,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
   </cols>
@@ -479,266 +479,130 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2">
-        <v>46183</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>94639182</v>
+        <v>95284508</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3">
-        <v>46183</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>86546118</v>
+        <v>95365565</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4">
-        <v>46183</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>86779944</v>
+        <v>95433452</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>46183</v>
+        <v>29</v>
       </c>
       <c r="D5">
-        <v>83316196</v>
+        <v>95648252</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6">
-        <v>46183</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>81792864</v>
+        <v>96300496</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>46183</v>
+        <v>29</v>
       </c>
       <c r="D7">
-        <v>94028248</v>
+        <v>96305022</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>46183</v>
+        <v>29</v>
       </c>
       <c r="D8">
-        <v>95488776</v>
+        <v>96534719</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9">
-        <v>46183</v>
+        <v>29</v>
       </c>
       <c r="D9">
-        <v>93476514</v>
+        <v>96561700</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>46183</v>
+        <v>29</v>
       </c>
       <c r="D10">
-        <v>76904727</v>
+        <v>96596045</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11">
-        <v>46183</v>
+        <v>29</v>
       </c>
       <c r="D11">
-        <v>115720162</v>
+        <v>96659511</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12">
-        <v>46183</v>
+        <v>29</v>
       </c>
       <c r="D12">
-        <v>222557966</v>
+        <v>96985666</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13">
-        <v>46183</v>
+        <v>29</v>
       </c>
       <c r="D13">
-        <v>789823306</v>
+        <v>97164816</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14">
-        <v>46183</v>
+        <v>29</v>
       </c>
       <c r="D14">
-        <v>85039945</v>
+        <v>451215559</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15">
-        <v>46183</v>
+        <v>29</v>
       </c>
       <c r="D15">
-        <v>906839661</v>
+        <v>451566114</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16">
-        <v>46183</v>
+        <v>29</v>
       </c>
       <c r="D16">
-        <v>593931173</v>
+        <v>594082986</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17">
-        <v>46183</v>
+        <v>29</v>
       </c>
       <c r="D17">
-        <v>190635789</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18">
-        <v>46183</v>
-      </c>
-      <c r="D18">
-        <v>745678793</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19">
-        <v>46183</v>
-      </c>
-      <c r="D19">
-        <v>81646677</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20">
-        <v>46183</v>
-      </c>
-      <c r="D20">
-        <v>93116574</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21">
-        <v>46183</v>
-      </c>
-      <c r="D21">
-        <v>86948624</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22">
-        <v>46183</v>
-      </c>
-      <c r="D22">
-        <v>82015735</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23">
-        <v>46183</v>
-      </c>
-      <c r="D23">
-        <v>94835103</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24">
-        <v>46183</v>
-      </c>
-      <c r="D24">
-        <v>92906207</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25">
-        <v>46183</v>
-      </c>
-      <c r="D25">
-        <v>83633828</v>
+        <v>882001140</v>
       </c>
     </row>
   </sheetData>

--- a/Flag/Flagar/lista_mos.xlsx
+++ b/Flag/Flagar/lista_mos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\le37118890\Desktop\codigos_amil\Codigos_Amil\Flag\Flagar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DCF01B8-DA0B-45EF-80BD-E9FE7D847D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3883DB1D-B9C8-465C-95E4-280E17E32ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="31">
   <si>
     <t>Flag</t>
   </si>
@@ -171,9 +171,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -454,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" bestFit="1" customWidth="1"/>
@@ -479,131 +480,393 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>9</v>
+      </c>
+      <c r="C2" s="2">
+        <v>46196</v>
       </c>
       <c r="D2">
-        <v>95284508</v>
+        <v>92865919</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>10</v>
+      </c>
+      <c r="C3" s="2">
+        <v>46196</v>
       </c>
       <c r="D3">
-        <v>95365565</v>
+        <v>95743588</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>10</v>
+      </c>
+      <c r="C4" s="2">
+        <v>46196</v>
       </c>
       <c r="D4">
-        <v>95433452</v>
+        <v>94651557</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>10</v>
+      </c>
+      <c r="C5" s="2">
+        <v>46196</v>
       </c>
       <c r="D5">
-        <v>95648252</v>
+        <v>92897609</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>10</v>
+      </c>
+      <c r="C6" s="2">
+        <v>46196</v>
       </c>
       <c r="D6">
-        <v>96300496</v>
+        <v>97713347</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>11</v>
+      </c>
+      <c r="C7" s="2">
+        <v>46196</v>
       </c>
       <c r="D7">
-        <v>96305022</v>
+        <v>97760180</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>12</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46196</v>
       </c>
       <c r="D8">
-        <v>96534719</v>
+        <v>92998114</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>12</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46196</v>
       </c>
       <c r="D9">
-        <v>96561700</v>
+        <v>96782963</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>12</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46196</v>
       </c>
       <c r="D10">
-        <v>96596045</v>
+        <v>96637052</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>12</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46196</v>
       </c>
       <c r="D11">
-        <v>96659511</v>
+        <v>97050888</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>14</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46196</v>
       </c>
       <c r="D12">
-        <v>96985666</v>
+        <v>95074125</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>14</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46196</v>
       </c>
       <c r="D13">
-        <v>97164816</v>
+        <v>96252961</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>15</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46196</v>
       </c>
       <c r="D14">
-        <v>451215559</v>
+        <v>93512690</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>15</v>
+      </c>
+      <c r="C15" s="2">
+        <v>46196</v>
       </c>
       <c r="D15">
-        <v>451566114</v>
+        <v>451929845</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>17</v>
+      </c>
+      <c r="C16" s="2">
+        <v>46196</v>
       </c>
       <c r="D16">
-        <v>594082986</v>
+        <v>83617517</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>18</v>
+      </c>
+      <c r="C17" s="2">
+        <v>46196</v>
       </c>
       <c r="D17">
-        <v>882001140</v>
-      </c>
+        <v>95711553</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="2">
+        <v>46196</v>
+      </c>
+      <c r="D18">
+        <v>95710405</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="2">
+        <v>46196</v>
+      </c>
+      <c r="D19">
+        <v>94722467</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="2">
+        <v>46196</v>
+      </c>
+      <c r="D20">
+        <v>89990991</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="2">
+        <v>46196</v>
+      </c>
+      <c r="D21">
+        <v>93823257</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="2">
+        <v>46196</v>
+      </c>
+      <c r="D22">
+        <v>82929624</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="2">
+        <v>46196</v>
+      </c>
+      <c r="D23">
+        <v>97864805</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="2">
+        <v>46196</v>
+      </c>
+      <c r="D24">
+        <v>85304054</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="2">
+        <v>46196</v>
+      </c>
+      <c r="D25">
+        <v>95739111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C29" s="2"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C30" s="2"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C31" s="2"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C32" s="2"/>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C33" s="2"/>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C34" s="2"/>
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C35" s="2"/>
+    </row>
+    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C36" s="2"/>
+    </row>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C37" s="2"/>
+    </row>
+    <row r="38" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C38" s="2"/>
+    </row>
+    <row r="39" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C39" s="2"/>
+    </row>
+    <row r="40" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C40" s="2"/>
+    </row>
+    <row r="41" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C41" s="2"/>
+    </row>
+    <row r="42" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C42" s="2"/>
+    </row>
+    <row r="43" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C43" s="2"/>
+    </row>
+    <row r="44" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C44" s="2"/>
+    </row>
+    <row r="45" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C45" s="2"/>
+    </row>
+    <row r="46" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C46" s="2"/>
+    </row>
+    <row r="47" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C47" s="2"/>
+    </row>
+    <row r="48" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C48" s="2"/>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C49" s="2"/>
+    </row>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C50" s="2"/>
+    </row>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C51" s="2"/>
+    </row>
+    <row r="52" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C52" s="2"/>
+    </row>
+    <row r="53" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C53" s="2"/>
+    </row>
+    <row r="54" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C54" s="2"/>
+    </row>
+    <row r="55" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C55" s="2"/>
+    </row>
+    <row r="56" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C56" s="2"/>
+    </row>
+    <row r="57" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C57" s="2"/>
+    </row>
+    <row r="58" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C58" s="2"/>
+    </row>
+    <row r="59" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C59" s="2"/>
+    </row>
+    <row r="60" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C60" s="2"/>
+    </row>
+    <row r="61" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C61" s="2"/>
+    </row>
+    <row r="62" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C62" s="2"/>
+    </row>
+    <row r="63" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C63" s="2"/>
+    </row>
+    <row r="64" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C64" s="2"/>
+    </row>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C65" s="2"/>
+    </row>
+    <row r="66" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C66" s="2"/>
+    </row>
+    <row r="67" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C67" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
